--- a/StudentManagementSystem/src/main/resources/StudentData_Upload_100_Records.xlsx
+++ b/StudentManagementSystem/src/main/resources/StudentData_Upload_100_Records.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suraj\git\finalproject\StudentManagementSystem\src\main\resources\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="4100" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Personal" sheetId="1" r:id="rId1"/>
@@ -12,7 +17,7 @@
     <sheet name="Attendance" sheetId="3" r:id="rId3"/>
     <sheet name="Sports" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -1198,8 +1203,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1262,6 +1267,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1308,7 +1321,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1340,9 +1353,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1374,6 +1388,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1549,11 +1564,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F101"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1573,7 +1588,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1593,7 +1608,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1613,7 +1628,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1633,7 +1648,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1653,7 +1668,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1673,7 +1688,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1693,7 +1708,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1713,7 +1728,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1733,7 +1748,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1753,7 +1768,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1773,7 +1788,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1793,7 +1808,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1813,7 +1828,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1833,7 +1848,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1853,7 +1868,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1873,7 +1888,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1893,7 +1908,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1913,7 +1928,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1933,7 +1948,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1953,7 +1968,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1973,7 +1988,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1993,7 +2008,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2013,7 +2028,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2033,7 +2048,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2053,7 +2068,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2073,7 +2088,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2093,7 +2108,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2113,7 +2128,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2133,7 +2148,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2153,7 +2168,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2173,7 +2188,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2193,7 +2208,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2213,7 +2228,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2233,7 +2248,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2253,7 +2268,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2273,7 +2288,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2293,7 +2308,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2313,7 +2328,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2333,7 +2348,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2353,7 +2368,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2373,7 +2388,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2393,7 +2408,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2413,7 +2428,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2433,7 +2448,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2453,7 +2468,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2473,7 +2488,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2493,7 +2508,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2513,7 +2528,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2533,7 +2548,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2553,7 +2568,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2573,7 +2588,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2593,7 +2608,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2613,7 +2628,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2633,7 +2648,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2653,7 +2668,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2673,7 +2688,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2693,7 +2708,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2713,7 +2728,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2733,7 +2748,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2753,7 +2768,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2773,7 +2788,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2793,7 +2808,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2813,7 +2828,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2833,7 +2848,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2853,7 +2868,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2873,7 +2888,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2893,7 +2908,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2913,7 +2928,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2933,7 +2948,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2953,7 +2968,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2973,7 +2988,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2993,7 +3008,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -3013,7 +3028,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -3033,7 +3048,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -3053,7 +3068,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -3073,7 +3088,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -3093,7 +3108,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -3113,7 +3128,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -3133,7 +3148,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -3153,7 +3168,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -3173,7 +3188,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -3193,7 +3208,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -3213,7 +3228,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
@@ -3233,7 +3248,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -3253,7 +3268,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -3273,7 +3288,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -3293,7 +3308,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -3313,7 +3328,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -3333,7 +3348,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -3353,7 +3368,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
@@ -3373,7 +3388,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
@@ -3393,7 +3408,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
@@ -3413,7 +3428,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -3433,7 +3448,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -3453,7 +3468,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -3473,7 +3488,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
@@ -3493,7 +3508,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -3513,7 +3528,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
@@ -3533,7 +3548,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
@@ -3553,7 +3568,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
@@ -3579,11 +3594,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C101"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3594,7 +3614,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3605,7 +3625,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3616,7 +3636,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3627,7 +3647,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3638,7 +3658,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3649,7 +3669,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3660,7 +3680,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3671,7 +3691,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3682,7 +3702,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3693,7 +3713,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3704,7 +3724,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3715,7 +3735,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3726,7 +3746,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3737,7 +3757,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3748,7 +3768,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3759,7 +3779,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3770,7 +3790,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3781,7 +3801,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3792,7 +3812,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3803,7 +3823,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3814,7 +3834,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3825,7 +3845,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3836,7 +3856,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3847,7 +3867,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3858,7 +3878,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3869,7 +3889,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3880,7 +3900,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3891,7 +3911,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3902,7 +3922,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3913,7 +3933,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3924,7 +3944,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3935,7 +3955,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3946,7 +3966,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3957,7 +3977,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3968,7 +3988,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3979,7 +3999,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3990,7 +4010,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4001,7 +4021,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4012,7 +4032,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4023,7 +4043,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4034,7 +4054,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4045,7 +4065,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -4056,7 +4076,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -4067,7 +4087,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -4078,7 +4098,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -4089,7 +4109,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -4100,7 +4120,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -4111,7 +4131,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -4122,7 +4142,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4133,7 +4153,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -4144,7 +4164,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -4155,7 +4175,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4166,7 +4186,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4177,7 +4197,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4188,7 +4208,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -4199,7 +4219,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4210,7 +4230,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4221,7 +4241,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4232,7 +4252,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4243,7 +4263,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4254,7 +4274,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4265,7 +4285,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4276,7 +4296,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4287,7 +4307,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4298,7 +4318,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4309,7 +4329,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4320,7 +4340,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4331,7 +4351,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4342,7 +4362,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4353,7 +4373,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4364,7 +4384,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4375,7 +4395,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4386,7 +4406,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4397,7 +4417,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4408,7 +4428,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4419,7 +4439,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4430,7 +4450,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4441,7 +4461,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -4452,7 +4472,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -4463,7 +4483,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -4474,7 +4494,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -4485,7 +4505,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -4496,7 +4516,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
@@ -4507,7 +4527,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -4518,7 +4538,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -4529,7 +4549,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -4540,7 +4560,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -4551,7 +4571,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -4562,7 +4582,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -4573,7 +4593,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
@@ -4584,7 +4604,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
@@ -4595,7 +4615,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
@@ -4606,7 +4626,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -4617,7 +4637,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -4628,7 +4648,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -4639,7 +4659,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
@@ -4650,7 +4670,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -4661,7 +4681,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
@@ -4672,7 +4692,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
@@ -4683,7 +4703,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
@@ -4700,11 +4720,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C101"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4715,7 +4740,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4726,7 +4751,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4737,7 +4762,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4748,7 +4773,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4759,7 +4784,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4770,7 +4795,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4781,7 +4806,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4792,7 +4817,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4803,7 +4828,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4814,7 +4839,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4825,7 +4850,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4836,7 +4861,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4847,7 +4872,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4858,7 +4883,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4869,7 +4894,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4880,7 +4905,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4891,7 +4916,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4902,7 +4927,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4913,7 +4938,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4924,7 +4949,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4935,7 +4960,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4946,7 +4971,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4957,7 +4982,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4968,7 +4993,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4979,7 +5004,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4990,7 +5015,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5001,7 +5026,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5012,7 +5037,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5023,7 +5048,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5034,7 +5059,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5045,7 +5070,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5056,7 +5081,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5067,7 +5092,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5078,7 +5103,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5089,7 +5114,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5100,7 +5125,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5111,7 +5136,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5122,7 +5147,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5133,7 +5158,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5144,7 +5169,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5155,7 +5180,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5166,7 +5191,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5177,7 +5202,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5188,7 +5213,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5199,7 +5224,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5210,7 +5235,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5221,7 +5246,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5232,7 +5257,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5243,7 +5268,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5254,7 +5279,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5265,7 +5290,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5276,7 +5301,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5287,7 +5312,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5298,7 +5323,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5309,7 +5334,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5320,7 +5345,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -5331,7 +5356,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -5342,7 +5367,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -5353,7 +5378,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -5364,7 +5389,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -5375,7 +5400,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -5386,7 +5411,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -5397,7 +5422,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -5408,7 +5433,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -5419,7 +5444,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -5430,7 +5455,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -5441,7 +5466,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -5452,7 +5477,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -5463,7 +5488,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -5474,7 +5499,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -5485,7 +5510,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -5496,7 +5521,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -5507,7 +5532,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -5518,7 +5543,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -5529,7 +5554,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -5540,7 +5565,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -5551,7 +5576,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -5562,7 +5587,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5573,7 +5598,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5584,7 +5609,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5595,7 +5620,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5606,7 +5631,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5617,7 +5642,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
@@ -5628,7 +5653,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -5639,7 +5664,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -5650,7 +5675,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -5661,7 +5686,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -5672,7 +5697,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -5683,7 +5708,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5694,7 +5719,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
@@ -5705,7 +5730,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5716,7 +5741,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5727,7 +5752,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5738,7 +5763,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5749,7 +5774,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -5760,7 +5785,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5771,7 +5796,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5782,7 +5807,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
@@ -5793,7 +5818,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
@@ -5804,7 +5829,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
@@ -5821,11 +5846,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D101"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5839,7 +5864,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5853,7 +5878,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5867,7 +5892,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5881,7 +5906,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5895,7 +5920,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5909,7 +5934,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5923,7 +5948,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5937,7 +5962,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5951,7 +5976,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5965,7 +5990,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5979,7 +6004,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5993,7 +6018,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -6007,7 +6032,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6021,7 +6046,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6035,7 +6060,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6049,7 +6074,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6063,7 +6088,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6077,7 +6102,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -6091,7 +6116,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -6105,7 +6130,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -6119,7 +6144,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -6133,7 +6158,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -6147,7 +6172,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -6161,7 +6186,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -6175,7 +6200,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -6189,7 +6214,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -6203,7 +6228,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -6217,7 +6242,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -6231,7 +6256,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -6245,7 +6270,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -6259,7 +6284,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -6273,7 +6298,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -6287,7 +6312,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -6301,7 +6326,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -6315,7 +6340,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -6329,7 +6354,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -6343,7 +6368,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -6357,7 +6382,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -6371,7 +6396,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -6385,7 +6410,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -6399,7 +6424,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -6413,7 +6438,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -6427,7 +6452,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -6441,7 +6466,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -6455,7 +6480,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -6469,7 +6494,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -6483,7 +6508,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -6497,7 +6522,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -6511,7 +6536,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -6525,7 +6550,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -6539,7 +6564,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6553,7 +6578,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -6567,7 +6592,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -6581,7 +6606,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -6595,7 +6620,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -6609,7 +6634,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6623,7 +6648,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6637,7 +6662,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6651,7 +6676,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6665,7 +6690,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6679,7 +6704,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -6693,7 +6718,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -6707,7 +6732,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -6721,7 +6746,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -6735,7 +6760,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -6749,7 +6774,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -6763,7 +6788,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -6777,7 +6802,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6791,7 +6816,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6805,7 +6830,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6819,7 +6844,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6833,7 +6858,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -6847,7 +6872,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -6861,7 +6886,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -6875,7 +6900,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -6889,7 +6914,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -6903,7 +6928,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -6917,7 +6942,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -6931,7 +6956,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -6945,7 +6970,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -6959,7 +6984,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -6973,7 +6998,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -6987,7 +7012,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
@@ -7001,7 +7026,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -7015,7 +7040,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -7029,7 +7054,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -7043,7 +7068,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -7057,7 +7082,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -7071,7 +7096,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -7085,7 +7110,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
@@ -7099,7 +7124,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
@@ -7113,7 +7138,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
@@ -7127,7 +7152,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -7141,7 +7166,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -7155,7 +7180,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -7169,7 +7194,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
@@ -7183,7 +7208,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -7197,7 +7222,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
@@ -7211,7 +7236,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
@@ -7225,7 +7250,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
